--- a/dist/成果/沟道纵断面成果表_AFAE900121E00000ZACS004.xlsx
+++ b/dist/成果/沟道纵断面成果表_AFAE900121E00000ZACS004.xlsx
@@ -794,7 +794,7 @@
         <v>33.103</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>33.27143124701863</v>
+        <v>33.5788902785103</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>115.565803</v>
@@ -822,7 +822,7 @@
         <v>32.599</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>32.7276610450213</v>
+        <v>33.02452221115753</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>115.566123</v>
@@ -850,7 +850,7 @@
         <v>32.223</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>32.29395838263902</v>
+        <v>32.70190989831824</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>115.56615</v>
@@ -878,7 +878,7 @@
         <v>31.769</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>32.20365653631481</v>
+        <v>31.83403828532275</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>115.566057</v>
@@ -906,7 +906,7 @@
         <v>31.514</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>31.99695649343627</v>
+        <v>31.72061006593398</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>115.56607</v>
@@ -934,7 +934,7 @@
         <v>31.197</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>31.21548930862227</v>
+        <v>31.52200472764024</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>115.566118</v>
@@ -962,7 +962,7 @@
         <v>30.626</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>30.8324429170991</v>
+        <v>31.01573978085147</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>115.566422</v>
@@ -990,7 +990,7 @@
         <v>29.676</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>29.67964833699013</v>
+        <v>29.7090998637744</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>115.566431</v>
@@ -1018,7 +1018,7 @@
         <v>28.49</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>28.92593279757204</v>
+        <v>28.78472155887769</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>115.566466</v>
@@ -1046,7 +1046,7 @@
         <v>28.464</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>28.48380065679543</v>
+        <v>28.73838600710975</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>115.566614</v>
@@ -1074,7 +1074,7 @@
         <v>28.438</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>28.66313024032583</v>
+        <v>28.55019011381819</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>115.566698</v>
@@ -1102,7 +1102,7 @@
         <v>28.412</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>28.60607701334296</v>
+        <v>28.41792565783282</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>115.566752</v>
@@ -1130,7 +1130,7 @@
         <v>28.386</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>28.43272964529024</v>
+        <v>28.717083648151</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>115.566793</v>
@@ -1158,7 +1158,7 @@
         <v>28.36</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>28.78822975833692</v>
+        <v>28.49908134937787</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>115.567003</v>
@@ -1186,7 +1186,7 @@
         <v>28.334</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>28.69757815641116</v>
+        <v>28.478953973016</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>115.567702</v>
@@ -1214,7 +1214,7 @@
         <v>28.308</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>28.35794425639122</v>
+        <v>28.68679431002014</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>115.568342</v>
@@ -1242,7 +1242,7 @@
         <v>28.282</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>28.64737746180364</v>
+        <v>28.54077103700641</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>115.569229</v>
@@ -1270,7 +1270,7 @@
         <v>28.256</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>28.43689552328953</v>
+        <v>28.52902135209904</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>115.569351</v>
@@ -1298,7 +1298,7 @@
         <v>28.23</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>28.46953648726959</v>
+        <v>28.46767746285292</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>115.569677</v>
@@ -1326,7 +1326,7 @@
         <v>28.204</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>28.3667728356062</v>
+        <v>28.61513408901612</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>115.57009</v>
@@ -1354,7 +1354,7 @@
         <v>28.178</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>28.35950084570743</v>
+        <v>28.4410450594683</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>115.570528</v>
@@ -1382,7 +1382,7 @@
         <v>28.163</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>28.30143940194567</v>
+        <v>28.28369596221805</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>115.570925</v>
@@ -1410,7 +1410,7 @@
         <v>28.171</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>28.61297848924294</v>
+        <v>28.34876617206349</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>115.571181</v>
@@ -1438,7 +1438,7 @@
         <v>27.951</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>28.3076243242991</v>
+        <v>27.96993266555096</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>115.571321</v>
@@ -1466,7 +1466,7 @@
         <v>27.866</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>28.05281098859857</v>
+        <v>28.28994072461879</v>
       </c>
       <c r="G35" s="23" t="n">
         <v>115.571413</v>
@@ -1494,7 +1494,7 @@
         <v>27.819</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>28.27774342019159</v>
+        <v>27.99898188516425</v>
       </c>
       <c r="G36" s="23" t="n">
         <v>115.571599</v>
@@ -1522,7 +1522,7 @@
         <v>27.778</v>
       </c>
       <c r="F37" s="22" t="n">
-        <v>27.91429970377273</v>
+        <v>27.9337315123976</v>
       </c>
       <c r="G37" s="23" t="n">
         <v>115.571717</v>
@@ -1550,7 +1550,7 @@
         <v>27.712</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>27.81983579084804</v>
+        <v>27.80681292440778</v>
       </c>
       <c r="G38" s="23" t="n">
         <v>115.572048</v>
@@ -1578,7 +1578,7 @@
         <v>27.625</v>
       </c>
       <c r="F39" s="22" t="n">
-        <v>27.68375335815613</v>
+        <v>27.74634511249632</v>
       </c>
       <c r="G39" s="23" t="n">
         <v>115.572129</v>
@@ -1606,7 +1606,7 @@
         <v>27.577</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>28.07782504531672</v>
+        <v>27.89743407821276</v>
       </c>
       <c r="G40" s="23" t="n">
         <v>115.572176</v>
@@ -1634,7 +1634,7 @@
         <v>27.549</v>
       </c>
       <c r="F41" s="22" t="n">
-        <v>27.91696218915528</v>
+        <v>27.77413727162926</v>
       </c>
       <c r="G41" s="23" t="n">
         <v>115.572438</v>
@@ -1658,16 +1658,16 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"85高程系,假定高程系"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
